--- a/results/Int Task Remove ACC -0.2/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC -0.2/Rando_6_permute.xlsx
@@ -440,47 +440,47 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6619128095468028</v>
+        <v>0.6805660941344186</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6521004345726702</v>
+        <v>0.688653974385505</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6678651904991837</v>
+        <v>0.6937383596606195</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.66716677013635</v>
+        <v>0.6923990020923869</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6664827205628752</v>
+        <v>0.6890937205398818</v>
       </c>
     </row>
     <row r="7">
@@ -490,597 +490,597 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6664827205628752</v>
+        <v>0.6890937205398818</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6667960037708951</v>
+        <v>0.6897202869559219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6687762985445265</v>
+        <v>0.6897202869559219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6693453818031316</v>
+        <v>0.6897202869559219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6736163804005426</v>
+        <v>0.6897202869559219</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6670000689797889</v>
+        <v>0.6910165321560783</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6682675726012278</v>
+        <v>0.691614356993401</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6609758340806144</v>
+        <v>0.6797814490354326</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6730789128785266</v>
+        <v>0.6794825366167713</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6728231128279414</v>
+        <v>0.6797958198247913</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.662941758064887</v>
+        <v>0.6769475293738935</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6613466004460693</v>
+        <v>0.6882257248626152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6533708123519808</v>
+        <v>0.6841501690004828</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6533708123519808</v>
+        <v>0.6710152675266148</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6522872548343335</v>
+        <v>0.6006415120369731</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6396007219884574</v>
+        <v>0.5996872916235543</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6321652755742568</v>
+        <v>0.5911395461129889</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6291732772297717</v>
+        <v>0.5876618150881792</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6428715136465015</v>
+        <v>0.5720034030029202</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6431445586443172</v>
+        <v>0.5502115380193603</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6459641075164977</v>
+        <v>0.5492573176059414</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6532558460371112</v>
+        <v>0.5672265526200823</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6706128854245705</v>
+        <v>0.5678962314041985</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6712394518406106</v>
+        <v>0.5790652088937941</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.672110321675749</v>
+        <v>0.5829798119151088</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6973971626313491</v>
+        <v>0.5912430157963716</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7044014853647881</v>
+        <v>0.5972844956427766</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7104113494746039</v>
+        <v>0.5920420316847164</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7056402474075096</v>
+        <v>0.5930824768342875</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7113828148352532</v>
+        <v>0.5930824768342875</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7249114759375503</v>
+        <v>0.574202133774804</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7752207353245499</v>
+        <v>0.6043721689544963</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7768302637327262</v>
+        <v>0.6161188521763123</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7787099629808466</v>
+        <v>0.6094105677036628</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7783966797728266</v>
+        <v>0.6066686210940194</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7873266882803338</v>
+        <v>0.5887424984479548</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7873266882803338</v>
+        <v>0.5839282840127843</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7427513738474627</v>
+        <v>0.5791399369984594</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7183641443057185</v>
+        <v>0.5727593065231887</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7329102572946127</v>
+        <v>0.5580349957462464</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7162775056908326</v>
+        <v>0.5648869881124831</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7307115265227289</v>
+        <v>0.5779385390080707</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7425760502172863</v>
+        <v>0.5860149226276701</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7061029868248603</v>
+        <v>0.564697293692948</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6824802832769998</v>
+        <v>0.5588167666873606</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6821382584902623</v>
+        <v>0.5610269940907314</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6411096548711228</v>
+        <v>0.5721413625807639</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6529828010392955</v>
+        <v>0.5646484330091284</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6467573750890989</v>
+        <v>0.5646484330091284</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6434118553263893</v>
+        <v>0.5710204410107839</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6434118553263893</v>
+        <v>0.5704226161734611</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6195419742015589</v>
+        <v>0.5454864224782139</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5560259593938977</v>
+        <v>0.574391828194339</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5684394472419581</v>
+        <v>0.5644328711687476</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5703335172794372</v>
+        <v>0.5645478374836173</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5641080913292406</v>
+        <v>0.5650048285852245</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5640362373824469</v>
+        <v>0.5653612241613207</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5659446782092847</v>
+        <v>0.5349813754569911</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5105625301786577</v>
+        <v>0.5340242808857005</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5010691867282886</v>
+        <v>0.5225017819778804</v>
       </c>
     </row>
     <row r="67">
@@ -1090,237 +1090,237 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5009829619921363</v>
+        <v>0.5080303970936516</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5016526407762526</v>
+        <v>0.5159515761881769</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5016382699868939</v>
+        <v>0.5109649122807017</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5016382699868939</v>
+        <v>0.5121174495872709</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5013106159895151</v>
+        <v>0.5114908831712308</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5009829619921363</v>
+        <v>0.5257610770044377</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5009829619921363</v>
+        <v>0.5381027109057046</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5013106159895151</v>
+        <v>0.5473891149893082</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5013106159895151</v>
+        <v>0.5467338069945507</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5009829619921363</v>
+        <v>0.5467338069945507</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5009829619921363</v>
+        <v>0.5254880320066221</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5013249867788738</v>
+        <v>0.5063288956335794</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5006696787841163</v>
+        <v>0.5061133337931987</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5003420247867375</v>
+        <v>0.5095881906601366</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5003276539973788</v>
+        <v>0.4964504150283967</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5003276539973788</v>
+        <v>0.5013134901473868</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5000143707893587</v>
+        <v>0.4979248580166011</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.5034030029201444</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5</v>
+        <v>0.5087661815088179</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5</v>
+        <v>0.5271952817824378</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.5286754730863856</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.4994222942677795</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.5047394863305051</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.4998304246855672</v>
       </c>
     </row>
   </sheetData>
